--- a/fuelprices.xlsx
+++ b/fuelprices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lucit-my.sharepoint.com/personal/jouko_teeriaho_lapinamk_fi/Documents/Tiedostot/GitHub/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="8_{17C23E18-6C08-424E-9A6E-75714FE7FC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE14565E-6DDF-48F4-ADE1-E97C719AE315}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{17C23E18-6C08-424E-9A6E-75714FE7FC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94A3295C-2CB7-4C23-92FF-D4B7843EBBDD}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="80" windowWidth="19110" windowHeight="10000" xr2:uid="{2E0E04A6-E858-429D-A294-47240510E5EA}"/>
+    <workbookView xWindow="330" yWindow="120" windowWidth="18870" windowHeight="9960" xr2:uid="{2E0E04A6-E858-429D-A294-47240510E5EA}"/>
   </bookViews>
   <sheets>
     <sheet name="fuel price comparison" sheetId="8" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>A table of daily fuel prices at two petrol stations during 1st quarter of year 2024</t>
   </si>
@@ -60,6 +60,48 @@
   </si>
   <si>
     <t>FUEL PRICES COMPARISON</t>
+  </si>
+  <si>
+    <t>Parittainen kahden otoksen t-testi keskiarvoille</t>
+  </si>
+  <si>
+    <t>Muuttuja 1</t>
+  </si>
+  <si>
+    <t>Muuttuja 2</t>
+  </si>
+  <si>
+    <t>Keskiarvo</t>
+  </si>
+  <si>
+    <t>Varianssi</t>
+  </si>
+  <si>
+    <t>Havainnot</t>
+  </si>
+  <si>
+    <t>Pearsonin korrelaatio</t>
+  </si>
+  <si>
+    <t>Arvioitu keskiarvojen ero</t>
+  </si>
+  <si>
+    <t>va</t>
+  </si>
+  <si>
+    <t>t Tunnusluvut</t>
+  </si>
+  <si>
+    <t>P(T&lt;=t) yksisuuntainen</t>
+  </si>
+  <si>
+    <t>t-kriittinen yksisuuntainen</t>
+  </si>
+  <si>
+    <t>P(T&lt;=t) kaksisuuntainen</t>
+  </si>
+  <si>
+    <t>t-kriittinen kaksisuuntainen</t>
   </si>
 </sst>
 </file>
@@ -70,7 +112,7 @@
     <numFmt numFmtId="164" formatCode="d\.m\.;@"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,6 +151,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -124,7 +174,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -162,11 +212,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -184,6 +254,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -699,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FAB5BEE-E6B6-4D1E-97F6-D6EA31967F80}">
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
@@ -1575,7 +1650,7 @@
         <v>1.976</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="6">
         <v>45003</v>
       </c>
@@ -1585,8 +1660,11 @@
       <c r="C81" s="7">
         <v>2.016</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="F81" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="6">
         <v>45004</v>
       </c>
@@ -1597,7 +1675,7 @@
         <v>1.946</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="6">
         <v>45005</v>
       </c>
@@ -1607,8 +1685,15 @@
       <c r="C83" s="7">
         <v>1.9659999999999997</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="F83" s="13"/>
+      <c r="G83" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H83" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="6">
         <v>45006</v>
       </c>
@@ -1618,8 +1703,17 @@
       <c r="C84" s="7">
         <v>2.016</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="F84" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G84" s="11">
+        <v>1.9813333333333332</v>
+      </c>
+      <c r="H84" s="11">
+        <v>1.9889111111111106</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" s="6">
         <v>45007</v>
       </c>
@@ -1629,8 +1723,17 @@
       <c r="C85" s="7">
         <v>1.996</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="F85" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G85" s="11">
+        <v>2.7015730337078651E-3</v>
+      </c>
+      <c r="H85" s="11">
+        <v>5.9324189762796483E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="6">
         <v>45008</v>
       </c>
@@ -1640,8 +1743,17 @@
       <c r="C86" s="7">
         <v>1.9659999999999997</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="F86" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="11">
+        <v>90</v>
+      </c>
+      <c r="H86" s="11">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="6">
         <v>45009</v>
       </c>
@@ -1651,8 +1763,15 @@
       <c r="C87" s="7">
         <v>1.9859999999999998</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="F87" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G87" s="11">
+        <v>0.797226162046339</v>
+      </c>
+      <c r="H87" s="11"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" s="6">
         <v>45010</v>
       </c>
@@ -1662,8 +1781,15 @@
       <c r="C88" s="7">
         <v>2.016</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="F88" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G88" s="11">
+        <v>0</v>
+      </c>
+      <c r="H88" s="11"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="6">
         <v>45011</v>
       </c>
@@ -1673,8 +1799,15 @@
       <c r="C89" s="7">
         <v>1.976</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="F89" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G89" s="11">
+        <v>89</v>
+      </c>
+      <c r="H89" s="11"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" s="6">
         <v>45012</v>
       </c>
@@ -1684,8 +1817,15 @@
       <c r="C90" s="7">
         <v>1.9859999999999998</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="F90" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G90" s="11">
+        <v>-1.5152757734909159</v>
+      </c>
+      <c r="H90" s="11"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="6">
         <v>45013</v>
       </c>
@@ -1695,8 +1835,15 @@
       <c r="C91" s="7">
         <v>1.9659999999999997</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="F91" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" s="11">
+        <v>6.662312189158455E-2</v>
+      </c>
+      <c r="H91" s="11"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="6">
         <v>45014</v>
       </c>
@@ -1706,8 +1853,15 @@
       <c r="C92" s="7">
         <v>1.9359999999999999</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="F92" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G92" s="11">
+        <v>1.6621553258697011</v>
+      </c>
+      <c r="H92" s="11"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="6">
         <v>45015</v>
       </c>
@@ -1717,8 +1871,15 @@
       <c r="C93" s="7">
         <v>1.996</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="F93" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G93" s="11">
+        <v>0.1332462437831691</v>
+      </c>
+      <c r="H93" s="11"/>
+    </row>
+    <row r="94" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="6">
         <v>45016</v>
       </c>
@@ -1728,8 +1889,15 @@
       <c r="C94" s="7">
         <v>1.9859999999999998</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="F94" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G94" s="12">
+        <v>1.986978699506285</v>
+      </c>
+      <c r="H94" s="12"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>3</v>
       </c>
@@ -1744,12 +1912,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Aptos"&amp;10&amp;K000000 Luottamuksellinen - Confidential (3Y)&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{4c60a66f-0a8d-446e-9ac0-836a00d84542}" enabled="0" method="" siteId="{4c60a66f-0a8d-446e-9ac0-836a00d84542}" removed="1"/>
+  <clbl:label id="{d823ee79-bdbf-4d11-a783-980929fd6733}" enabled="1" method="Standard" siteId="{4c60a66f-0a8d-446e-9ac0-836a00d84542}" removed="0"/>
 </clbl:labelList>
 </file>
--- a/fuelprices.xlsx
+++ b/fuelprices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lucit-my.sharepoint.com/personal/jouko_teeriaho_lapinamk_fi/Documents/Tiedostot/GitHub/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{17C23E18-6C08-424E-9A6E-75714FE7FC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94A3295C-2CB7-4C23-92FF-D4B7843EBBDD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B68BA5E-CDEB-4D25-B333-584820A725A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="120" windowWidth="18870" windowHeight="9960" xr2:uid="{2E0E04A6-E858-429D-A294-47240510E5EA}"/>
+    <workbookView xWindow="760" yWindow="120" windowWidth="16150" windowHeight="9960" xr2:uid="{2E0E04A6-E858-429D-A294-47240510E5EA}"/>
   </bookViews>
   <sheets>
     <sheet name="fuel price comparison" sheetId="8" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>A table of daily fuel prices at two petrol stations during 1st quarter of year 2024</t>
   </si>
@@ -61,48 +61,6 @@
   <si>
     <t>FUEL PRICES COMPARISON</t>
   </si>
-  <si>
-    <t>Parittainen kahden otoksen t-testi keskiarvoille</t>
-  </si>
-  <si>
-    <t>Muuttuja 1</t>
-  </si>
-  <si>
-    <t>Muuttuja 2</t>
-  </si>
-  <si>
-    <t>Keskiarvo</t>
-  </si>
-  <si>
-    <t>Varianssi</t>
-  </si>
-  <si>
-    <t>Havainnot</t>
-  </si>
-  <si>
-    <t>Pearsonin korrelaatio</t>
-  </si>
-  <si>
-    <t>Arvioitu keskiarvojen ero</t>
-  </si>
-  <si>
-    <t>va</t>
-  </si>
-  <si>
-    <t>t Tunnusluvut</t>
-  </si>
-  <si>
-    <t>P(T&lt;=t) yksisuuntainen</t>
-  </si>
-  <si>
-    <t>t-kriittinen yksisuuntainen</t>
-  </si>
-  <si>
-    <t>P(T&lt;=t) kaksisuuntainen</t>
-  </si>
-  <si>
-    <t>t-kriittinen kaksisuuntainen</t>
-  </si>
 </sst>
 </file>
 
@@ -112,7 +70,7 @@
     <numFmt numFmtId="164" formatCode="d\.m\.;@"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,14 +109,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -174,7 +124,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -212,31 +162,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -254,11 +184,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -774,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FAB5BEE-E6B6-4D1E-97F6-D6EA31967F80}">
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
@@ -1650,7 +1575,7 @@
         <v>1.976</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="6">
         <v>45003</v>
       </c>
@@ -1660,11 +1585,8 @@
       <c r="C81" s="7">
         <v>2.016</v>
       </c>
-      <c r="F81" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="6">
         <v>45004</v>
       </c>
@@ -1675,7 +1597,7 @@
         <v>1.946</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="6">
         <v>45005</v>
       </c>
@@ -1685,15 +1607,8 @@
       <c r="C83" s="7">
         <v>1.9659999999999997</v>
       </c>
-      <c r="F83" s="13"/>
-      <c r="G83" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="H83" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="6">
         <v>45006</v>
       </c>
@@ -1703,17 +1618,8 @@
       <c r="C84" s="7">
         <v>2.016</v>
       </c>
-      <c r="F84" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G84" s="11">
-        <v>1.9813333333333332</v>
-      </c>
-      <c r="H84" s="11">
-        <v>1.9889111111111106</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="6">
         <v>45007</v>
       </c>
@@ -1723,17 +1629,8 @@
       <c r="C85" s="7">
         <v>1.996</v>
       </c>
-      <c r="F85" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G85" s="11">
-        <v>2.7015730337078651E-3</v>
-      </c>
-      <c r="H85" s="11">
-        <v>5.9324189762796483E-3</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="6">
         <v>45008</v>
       </c>
@@ -1743,17 +1640,8 @@
       <c r="C86" s="7">
         <v>1.9659999999999997</v>
       </c>
-      <c r="F86" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G86" s="11">
-        <v>90</v>
-      </c>
-      <c r="H86" s="11">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="6">
         <v>45009</v>
       </c>
@@ -1763,15 +1651,8 @@
       <c r="C87" s="7">
         <v>1.9859999999999998</v>
       </c>
-      <c r="F87" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G87" s="11">
-        <v>0.797226162046339</v>
-      </c>
-      <c r="H87" s="11"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="6">
         <v>45010</v>
       </c>
@@ -1781,15 +1662,8 @@
       <c r="C88" s="7">
         <v>2.016</v>
       </c>
-      <c r="F88" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G88" s="11">
-        <v>0</v>
-      </c>
-      <c r="H88" s="11"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="6">
         <v>45011</v>
       </c>
@@ -1799,15 +1673,8 @@
       <c r="C89" s="7">
         <v>1.976</v>
       </c>
-      <c r="F89" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G89" s="11">
-        <v>89</v>
-      </c>
-      <c r="H89" s="11"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="6">
         <v>45012</v>
       </c>
@@ -1817,15 +1684,8 @@
       <c r="C90" s="7">
         <v>1.9859999999999998</v>
       </c>
-      <c r="F90" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G90" s="11">
-        <v>-1.5152757734909159</v>
-      </c>
-      <c r="H90" s="11"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="6">
         <v>45013</v>
       </c>
@@ -1835,15 +1695,8 @@
       <c r="C91" s="7">
         <v>1.9659999999999997</v>
       </c>
-      <c r="F91" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G91" s="11">
-        <v>6.662312189158455E-2</v>
-      </c>
-      <c r="H91" s="11"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="6">
         <v>45014</v>
       </c>
@@ -1853,15 +1706,8 @@
       <c r="C92" s="7">
         <v>1.9359999999999999</v>
       </c>
-      <c r="F92" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G92" s="11">
-        <v>1.6621553258697011</v>
-      </c>
-      <c r="H92" s="11"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="6">
         <v>45015</v>
       </c>
@@ -1871,15 +1717,8 @@
       <c r="C93" s="7">
         <v>1.996</v>
       </c>
-      <c r="F93" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G93" s="11">
-        <v>0.1332462437831691</v>
-      </c>
-      <c r="H93" s="11"/>
-    </row>
-    <row r="94" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="6">
         <v>45016</v>
       </c>
@@ -1889,15 +1728,8 @@
       <c r="C94" s="7">
         <v>1.9859999999999998</v>
       </c>
-      <c r="F94" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G94" s="12">
-        <v>1.986978699506285</v>
-      </c>
-      <c r="H94" s="12"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>3</v>
       </c>
